--- a/backend/tests_v1/fixtures/test_equity_jan_fixture.xlsx
+++ b/backend/tests_v1/fixtures/test_equity_jan_fixture.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <name val="Calibri"/>
@@ -46,8 +48,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,10 +452,8 @@
           <t>Supplier payment</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>05-01-2025</t>
-        </is>
+      <c r="B2" s="1" t="n">
+        <v>45662</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -471,10 +472,8 @@
           <t>Customer receipt</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>08-01-2025</t>
-        </is>
+      <c r="B3" s="1" t="n">
+        <v>45665</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -493,10 +492,8 @@
           <t>Bank charge</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>12-01-2025</t>
-        </is>
+      <c r="B4" s="1" t="n">
+        <v>45669</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -515,10 +512,8 @@
           <t>Payroll</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>15-01-2025</t>
-        </is>
+      <c r="B5" s="1" t="n">
+        <v>45672</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -537,10 +532,8 @@
           <t>Deposit</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>20-01-2025</t>
-        </is>
+      <c r="B6" s="1" t="n">
+        <v>45677</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -559,10 +552,8 @@
           <t>Transfer out</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>22-01-2025</t>
-        </is>
+      <c r="B7" s="1" t="n">
+        <v>45679</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -581,10 +572,8 @@
           <t>Interest</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>28-01-2025</t>
-        </is>
+      <c r="B8" s="1" t="n">
+        <v>45685</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -603,10 +592,8 @@
           <t>Opening top-up</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>31-01-2025</t>
-        </is>
+      <c r="B9" s="1" t="n">
+        <v>45688</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
